--- a/01-Planificación y analisis/Análisis/Matriz de riesgos.xlsx
+++ b/01-Planificación y analisis/Análisis/Matriz de riesgos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Estudio\Iberoamericana\Analisis y diseño de sistemas\Repositorio\01-planificacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Estudio\Iberoamericana\Analisis y diseño de sistemas\Repositorio\01-Planificación y analisis\Análisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAB44CE-E2E1-45A3-9D90-A0E4753FB508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2150AF00-CE1E-4D26-B181-AC44CDA95F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4040E105-3CB9-4BD6-8BA7-81DF2C624CCA}"/>
   </bookViews>
@@ -427,22 +427,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -837,12 +837,12 @@
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="10"/>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
@@ -871,7 +871,7 @@
       <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -888,7 +888,7 @@
       <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -905,7 +905,7 @@
       <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -922,7 +922,7 @@
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -939,7 +939,7 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <v>3</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -956,7 +956,7 @@
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>4</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -973,7 +973,7 @@
       <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="14">
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
